--- a/summary_stats/chuuchuu_summary_2025_08.xlsx
+++ b/summary_stats/chuuchuu_summary_2025_08.xlsx
@@ -980,19 +980,19 @@
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O7" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P7" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q7" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S7" t="n">
         <v>32</v>
@@ -1375,25 +1375,25 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
         <v>2</v>
@@ -1454,25 +1454,25 @@
         <v>91</v>
       </c>
       <c r="N13" t="n">
-        <v>1135</v>
+        <v>1108</v>
       </c>
       <c r="O13" t="n">
-        <v>989</v>
+        <v>963</v>
       </c>
       <c r="P13" t="n">
-        <v>899</v>
+        <v>875</v>
       </c>
       <c r="Q13" t="n">
-        <v>690</v>
+        <v>667</v>
       </c>
       <c r="R13" t="n">
-        <v>544</v>
+        <v>524</v>
       </c>
       <c r="S13" t="n">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="T13" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="U13" t="n">
         <v>2115</v>
@@ -1612,22 +1612,22 @@
         <v>33</v>
       </c>
       <c r="N15" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="O15" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P15" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="Q15" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="R15" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="S15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T15" t="n">
         <v>25</v>
@@ -1691,25 +1691,25 @@
         <v>725</v>
       </c>
       <c r="N16" t="n">
-        <v>2336</v>
+        <v>2072</v>
       </c>
       <c r="O16" t="n">
-        <v>2009</v>
+        <v>1770</v>
       </c>
       <c r="P16" t="n">
-        <v>1885</v>
+        <v>1653</v>
       </c>
       <c r="Q16" t="n">
-        <v>1517</v>
+        <v>1308</v>
       </c>
       <c r="R16" t="n">
-        <v>1181</v>
+        <v>999</v>
       </c>
       <c r="S16" t="n">
-        <v>595</v>
+        <v>477</v>
       </c>
       <c r="T16" t="n">
-        <v>171</v>
+        <v>121</v>
       </c>
       <c r="U16" t="n">
         <v>4015</v>
@@ -1770,25 +1770,25 @@
         <v>95</v>
       </c>
       <c r="N17" t="n">
-        <v>1118</v>
+        <v>1095</v>
       </c>
       <c r="O17" t="n">
-        <v>895</v>
+        <v>873</v>
       </c>
       <c r="P17" t="n">
-        <v>806</v>
+        <v>787</v>
       </c>
       <c r="Q17" t="n">
-        <v>599</v>
+        <v>582</v>
       </c>
       <c r="R17" t="n">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="S17" t="n">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="T17" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="U17" t="n">
         <v>1958</v>
@@ -1849,25 +1849,25 @@
         <v>1771</v>
       </c>
       <c r="N18" t="n">
-        <v>8392</v>
+        <v>7794</v>
       </c>
       <c r="O18" t="n">
-        <v>7372</v>
+        <v>6808</v>
       </c>
       <c r="P18" t="n">
-        <v>6929</v>
+        <v>6379</v>
       </c>
       <c r="Q18" t="n">
-        <v>5503</v>
+        <v>5003</v>
       </c>
       <c r="R18" t="n">
-        <v>4291</v>
+        <v>3866</v>
       </c>
       <c r="S18" t="n">
-        <v>2196</v>
+        <v>1902</v>
       </c>
       <c r="T18" t="n">
-        <v>691</v>
+        <v>567</v>
       </c>
       <c r="U18" t="n">
         <v>13251</v>
@@ -1928,25 +1928,25 @@
         <v>259</v>
       </c>
       <c r="N19" t="n">
-        <v>2555</v>
+        <v>2451</v>
       </c>
       <c r="O19" t="n">
-        <v>2204</v>
+        <v>2103</v>
       </c>
       <c r="P19" t="n">
-        <v>2064</v>
+        <v>1965</v>
       </c>
       <c r="Q19" t="n">
-        <v>1620</v>
+        <v>1529</v>
       </c>
       <c r="R19" t="n">
-        <v>1192</v>
+        <v>1110</v>
       </c>
       <c r="S19" t="n">
-        <v>575</v>
+        <v>519</v>
       </c>
       <c r="T19" t="n">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="U19" t="n">
         <v>3765</v>
@@ -2244,25 +2244,25 @@
         <v>40</v>
       </c>
       <c r="N23" t="n">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="O23" t="n">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="P23" t="n">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="Q23" t="n">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="R23" t="n">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="S23" t="n">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="T23" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="U23" t="n">
         <v>785</v>
@@ -2402,22 +2402,22 @@
         <v>22</v>
       </c>
       <c r="N25" t="n">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="O25" t="n">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="P25" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q25" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="R25" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="S25" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="T25" t="n">
         <v>4</v>
@@ -2481,25 +2481,25 @@
         <v>31</v>
       </c>
       <c r="N26" t="n">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="O26" t="n">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="P26" t="n">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="Q26" t="n">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="R26" t="n">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="S26" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="T26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U26" t="n">
         <v>405</v>
@@ -3113,25 +3113,25 @@
         <v>2</v>
       </c>
       <c r="N34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U34" t="n">
         <v>25</v>
@@ -3192,25 +3192,25 @@
         <v>572</v>
       </c>
       <c r="N35" t="n">
-        <v>878</v>
+        <v>803</v>
       </c>
       <c r="O35" t="n">
-        <v>867</v>
+        <v>792</v>
       </c>
       <c r="P35" t="n">
-        <v>864</v>
+        <v>789</v>
       </c>
       <c r="Q35" t="n">
-        <v>650</v>
+        <v>594</v>
       </c>
       <c r="R35" t="n">
-        <v>526</v>
+        <v>476</v>
       </c>
       <c r="S35" t="n">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="T35" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="U35" t="n">
         <v>3349</v>
@@ -3271,25 +3271,25 @@
         <v>37</v>
       </c>
       <c r="N36" t="n">
-        <v>352</v>
+        <v>331</v>
       </c>
       <c r="O36" t="n">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="P36" t="n">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="Q36" t="n">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="R36" t="n">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="S36" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="T36" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="U36" t="n">
         <v>533</v>
@@ -3350,25 +3350,25 @@
         <v>14</v>
       </c>
       <c r="N37" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="O37" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="P37" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q37" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R37" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U37" t="n">
         <v>55</v>
@@ -4140,22 +4140,22 @@
         <v>3360</v>
       </c>
       <c r="N47" t="n">
-        <v>3845</v>
+        <v>3712</v>
       </c>
       <c r="O47" t="n">
-        <v>2234</v>
+        <v>2135</v>
       </c>
       <c r="P47" t="n">
-        <v>1805</v>
+        <v>1719</v>
       </c>
       <c r="Q47" t="n">
-        <v>892</v>
+        <v>845</v>
       </c>
       <c r="R47" t="n">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="S47" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="T47" t="n">
         <v>2</v>
@@ -4219,22 +4219,22 @@
         <v>21</v>
       </c>
       <c r="N48" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="O48" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="P48" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Q48" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R48" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="S48" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T48" t="n">
         <v>17</v>
@@ -4298,22 +4298,22 @@
         <v>375</v>
       </c>
       <c r="N49" t="n">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="O49" t="n">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="P49" t="n">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="Q49" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="R49" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T49" t="n">
         <v>0</v>
@@ -4377,22 +4377,22 @@
         <v>4</v>
       </c>
       <c r="N50" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="O50" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P50" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Q50" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R50" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="S50" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="T50" t="n">
         <v>10</v>
@@ -4456,13 +4456,13 @@
         <v>6</v>
       </c>
       <c r="N51" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O51" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P51" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q51" t="n">
         <v>77</v>
@@ -4614,19 +4614,19 @@
         <v>211</v>
       </c>
       <c r="N53" t="n">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="O53" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="P53" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="Q53" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="R53" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -4693,19 +4693,19 @@
         <v>4062</v>
       </c>
       <c r="N54" t="n">
-        <v>4913</v>
+        <v>4796</v>
       </c>
       <c r="O54" t="n">
-        <v>2302</v>
+        <v>2236</v>
       </c>
       <c r="P54" t="n">
-        <v>1705</v>
+        <v>1654</v>
       </c>
       <c r="Q54" t="n">
-        <v>672</v>
+        <v>653</v>
       </c>
       <c r="R54" t="n">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="S54" t="n">
         <v>24</v>
@@ -4851,19 +4851,19 @@
         <v>899</v>
       </c>
       <c r="N56" t="n">
-        <v>1374</v>
+        <v>1342</v>
       </c>
       <c r="O56" t="n">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="P56" t="n">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="Q56" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="R56" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="S56" t="n">
         <v>8</v>
@@ -5404,22 +5404,22 @@
         <v>178</v>
       </c>
       <c r="N63" t="n">
-        <v>357</v>
+        <v>323</v>
       </c>
       <c r="O63" t="n">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="P63" t="n">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="Q63" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="R63" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="S63" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="T63" t="n">
         <v>12</v>
@@ -5957,25 +5957,25 @@
         <v>111</v>
       </c>
       <c r="N70" t="n">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="O70" t="n">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="P70" t="n">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="Q70" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="R70" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S70" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U70" t="n">
         <v>2041</v>
@@ -6115,25 +6115,25 @@
         <v>18</v>
       </c>
       <c r="N72" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="O72" t="n">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="P72" t="n">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="Q72" t="n">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="R72" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="S72" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T72" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U72" t="n">
         <v>909</v>
@@ -6194,22 +6194,22 @@
         <v>7</v>
       </c>
       <c r="N73" t="n">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="O73" t="n">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="P73" t="n">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="Q73" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R73" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="S73" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="T73" t="n">
         <v>26</v>
@@ -6510,25 +6510,25 @@
         <v>31</v>
       </c>
       <c r="N77" t="n">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="O77" t="n">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="P77" t="n">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="Q77" t="n">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="R77" t="n">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="S77" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="T77" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="U77" t="n">
         <v>1836</v>
@@ -7142,22 +7142,22 @@
         <v>57</v>
       </c>
       <c r="N85" t="n">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="O85" t="n">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="P85" t="n">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="Q85" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="R85" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="S85" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T85" t="n">
         <v>21</v>
@@ -7616,19 +7616,19 @@
         <v>292</v>
       </c>
       <c r="N91" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O91" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P91" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q91" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="R91" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="S91" t="n">
         <v>52</v>
@@ -8485,25 +8485,25 @@
         <v>2</v>
       </c>
       <c r="N102" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O102" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P102" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q102" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R102" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T102" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U102" t="n">
         <v>53</v>
@@ -8643,19 +8643,19 @@
         <v>23</v>
       </c>
       <c r="N104" t="n">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="O104" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="P104" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="Q104" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="R104" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S104" t="n">
         <v>13</v>
@@ -8722,25 +8722,25 @@
         <v>434</v>
       </c>
       <c r="N105" t="n">
-        <v>4431</v>
+        <v>4335</v>
       </c>
       <c r="O105" t="n">
-        <v>2659</v>
+        <v>2568</v>
       </c>
       <c r="P105" t="n">
-        <v>2200</v>
+        <v>2117</v>
       </c>
       <c r="Q105" t="n">
-        <v>1163</v>
+        <v>1087</v>
       </c>
       <c r="R105" t="n">
-        <v>636</v>
+        <v>575</v>
       </c>
       <c r="S105" t="n">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="T105" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="U105" t="n">
         <v>28452</v>
@@ -8801,25 +8801,25 @@
         <v>62</v>
       </c>
       <c r="N106" t="n">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="O106" t="n">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="P106" t="n">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="Q106" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="R106" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U106" t="n">
         <v>3886</v>
@@ -8959,22 +8959,22 @@
         <v>7</v>
       </c>
       <c r="N108" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="O108" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P108" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="Q108" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R108" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="S108" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T108" t="n">
         <v>3</v>
@@ -9038,22 +9038,22 @@
         <v>73</v>
       </c>
       <c r="N109" t="n">
-        <v>1709</v>
+        <v>1702</v>
       </c>
       <c r="O109" t="n">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="P109" t="n">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="Q109" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="R109" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="S109" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="T109" t="n">
         <v>0</v>
@@ -9354,25 +9354,25 @@
         <v>28</v>
       </c>
       <c r="N113" t="n">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="O113" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="P113" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="Q113" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="R113" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U113" t="n">
         <v>2574</v>
@@ -9512,25 +9512,25 @@
         <v>170</v>
       </c>
       <c r="N115" t="n">
-        <v>2355</v>
+        <v>2320</v>
       </c>
       <c r="O115" t="n">
-        <v>1237</v>
+        <v>1208</v>
       </c>
       <c r="P115" t="n">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="Q115" t="n">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="R115" t="n">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="S115" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="T115" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U115" t="n">
         <v>25688</v>
@@ -9591,19 +9591,19 @@
         <v>42</v>
       </c>
       <c r="N116" t="n">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="O116" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="P116" t="n">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="Q116" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R116" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S116" t="n">
         <v>6</v>
@@ -10065,25 +10065,25 @@
         <v>6</v>
       </c>
       <c r="N122" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O122" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P122" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q122" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="R122" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S122" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="T122" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U122" t="n">
         <v>688</v>
@@ -10223,25 +10223,25 @@
         <v>37</v>
       </c>
       <c r="N124" t="n">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="O124" t="n">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="P124" t="n">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="Q124" t="n">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="R124" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="S124" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="T124" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="U124" t="n">
         <v>1930</v>
@@ -10381,25 +10381,25 @@
         <v>5</v>
       </c>
       <c r="N126" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O126" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P126" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q126" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R126" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S126" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U126" t="n">
         <v>187</v>
@@ -10539,19 +10539,19 @@
         <v>3</v>
       </c>
       <c r="N128" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O128" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P128" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q128" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R128" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S128" t="n">
         <v>23</v>
@@ -10855,25 +10855,25 @@
         <v>157</v>
       </c>
       <c r="N132" t="n">
-        <v>3729</v>
+        <v>3669</v>
       </c>
       <c r="O132" t="n">
-        <v>2322</v>
+        <v>2268</v>
       </c>
       <c r="P132" t="n">
-        <v>2321</v>
+        <v>2267</v>
       </c>
       <c r="Q132" t="n">
-        <v>1723</v>
+        <v>1674</v>
       </c>
       <c r="R132" t="n">
-        <v>1344</v>
+        <v>1296</v>
       </c>
       <c r="S132" t="n">
-        <v>712</v>
+        <v>671</v>
       </c>
       <c r="T132" t="n">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="U132" t="n">
         <v>13609</v>
@@ -10934,25 +10934,25 @@
         <v>13</v>
       </c>
       <c r="N133" t="n">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="O133" t="n">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="P133" t="n">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="Q133" t="n">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="R133" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="S133" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="T133" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="U133" t="n">
         <v>927</v>
@@ -11487,25 +11487,25 @@
         <v>13</v>
       </c>
       <c r="N140" t="n">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="O140" t="n">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="P140" t="n">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Q140" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R140" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="S140" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="T140" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U140" t="n">
         <v>1323</v>
@@ -11724,25 +11724,25 @@
         <v>6</v>
       </c>
       <c r="N143" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O143" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P143" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q143" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R143" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S143" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U143" t="n">
         <v>46</v>
@@ -11803,25 +11803,25 @@
         <v>4</v>
       </c>
       <c r="N144" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="O144" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="P144" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Q144" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="R144" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="S144" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="T144" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U144" t="n">
         <v>537</v>
@@ -11882,7 +11882,7 @@
         <v>3</v>
       </c>
       <c r="N145" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O145" t="n">
         <v>184</v>
@@ -11961,25 +11961,25 @@
         <v>26</v>
       </c>
       <c r="N146" t="n">
-        <v>1897</v>
+        <v>1891</v>
       </c>
       <c r="O146" t="n">
-        <v>1443</v>
+        <v>1438</v>
       </c>
       <c r="P146" t="n">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="Q146" t="n">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="R146" t="n">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="S146" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="T146" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="U146" t="n">
         <v>5769</v>
@@ -12040,22 +12040,22 @@
         <v>47</v>
       </c>
       <c r="N147" t="n">
-        <v>1286</v>
+        <v>1278</v>
       </c>
       <c r="O147" t="n">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="P147" t="n">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="Q147" t="n">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="R147" t="n">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="S147" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="T147" t="n">
         <v>106</v>
@@ -12435,13 +12435,13 @@
         <v>104</v>
       </c>
       <c r="N152" t="n">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="O152" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P152" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q152" t="n">
         <v>35</v>
@@ -12830,25 +12830,25 @@
         <v>3781</v>
       </c>
       <c r="N157" t="n">
-        <v>31452</v>
+        <v>31199</v>
       </c>
       <c r="O157" t="n">
-        <v>17130</v>
+        <v>16927</v>
       </c>
       <c r="P157" t="n">
-        <v>13499</v>
+        <v>13318</v>
       </c>
       <c r="Q157" t="n">
-        <v>7093</v>
+        <v>6959</v>
       </c>
       <c r="R157" t="n">
-        <v>4313</v>
+        <v>4216</v>
       </c>
       <c r="S157" t="n">
-        <v>1524</v>
+        <v>1478</v>
       </c>
       <c r="T157" t="n">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="U157" t="n">
         <v>201345</v>
@@ -12909,25 +12909,25 @@
         <v>248</v>
       </c>
       <c r="N158" t="n">
-        <v>798</v>
+        <v>788</v>
       </c>
       <c r="O158" t="n">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="P158" t="n">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="Q158" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="R158" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="S158" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T158" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U158" t="n">
         <v>4205</v>
@@ -13620,25 +13620,25 @@
         <v>8</v>
       </c>
       <c r="N167" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="O167" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="P167" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="Q167" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R167" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="S167" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T167" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U167" t="n">
         <v>267</v>
@@ -14252,19 +14252,19 @@
         <v>1</v>
       </c>
       <c r="N175" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O175" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P175" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q175" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R175" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S175" t="n">
         <v>17</v>
@@ -14718,25 +14718,25 @@
         <v>16</v>
       </c>
       <c r="N181" t="n">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="O181" t="n">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="P181" t="n">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="Q181" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="R181" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="S181" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="T181" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="U181" t="n">
         <v>312</v>
@@ -15328,25 +15328,25 @@
         <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P3" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q3" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="R3" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="S3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V3" t="n">
         <v>684</v>
@@ -15664,19 +15664,19 @@
         <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P7" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q7" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R7" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="S7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="T7" t="n">
         <v>23</v>
@@ -16084,25 +16084,25 @@
         <v>37</v>
       </c>
       <c r="O12" t="n">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="P12" t="n">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="Q12" t="n">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="R12" t="n">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="S12" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="T12" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="U12" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="V12" t="n">
         <v>1930</v>
@@ -16252,25 +16252,25 @@
         <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
         <v>187</v>
@@ -16420,25 +16420,25 @@
         <v>157</v>
       </c>
       <c r="O16" t="n">
-        <v>3729</v>
+        <v>3669</v>
       </c>
       <c r="P16" t="n">
-        <v>2322</v>
+        <v>2268</v>
       </c>
       <c r="Q16" t="n">
-        <v>2321</v>
+        <v>2267</v>
       </c>
       <c r="R16" t="n">
-        <v>1723</v>
+        <v>1674</v>
       </c>
       <c r="S16" t="n">
-        <v>1344</v>
+        <v>1296</v>
       </c>
       <c r="T16" t="n">
-        <v>712</v>
+        <v>671</v>
       </c>
       <c r="U16" t="n">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="V16" t="n">
         <v>13609</v>
@@ -16504,25 +16504,25 @@
         <v>13</v>
       </c>
       <c r="O17" t="n">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="P17" t="n">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="Q17" t="n">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="R17" t="n">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="S17" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="T17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="U17" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="V17" t="n">
         <v>864</v>
@@ -16798,25 +16798,25 @@
         <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="P2" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="Q2" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="R2" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="S2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="T2" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="U2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V2" t="n">
         <v>371</v>
@@ -17218,22 +17218,22 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U7" t="n">
         <v>2</v>
@@ -17302,16 +17302,16 @@
         <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -17386,16 +17386,16 @@
         <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -17470,25 +17470,25 @@
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>2</v>
@@ -17554,25 +17554,25 @@
         <v>722</v>
       </c>
       <c r="O11" t="n">
-        <v>2318</v>
+        <v>2054</v>
       </c>
       <c r="P11" t="n">
-        <v>1993</v>
+        <v>1754</v>
       </c>
       <c r="Q11" t="n">
-        <v>1871</v>
+        <v>1639</v>
       </c>
       <c r="R11" t="n">
-        <v>1509</v>
+        <v>1300</v>
       </c>
       <c r="S11" t="n">
-        <v>1178</v>
+        <v>996</v>
       </c>
       <c r="T11" t="n">
-        <v>595</v>
+        <v>477</v>
       </c>
       <c r="U11" t="n">
-        <v>171</v>
+        <v>121</v>
       </c>
       <c r="V11" t="n">
         <v>3997</v>
@@ -17638,25 +17638,25 @@
         <v>43</v>
       </c>
       <c r="O12" t="n">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="P12" t="n">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="Q12" t="n">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="R12" t="n">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="S12" t="n">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="T12" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="U12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="V12" t="n">
         <v>478</v>
@@ -17722,25 +17722,25 @@
         <v>1771</v>
       </c>
       <c r="O13" t="n">
-        <v>8391</v>
+        <v>7793</v>
       </c>
       <c r="P13" t="n">
-        <v>7371</v>
+        <v>6807</v>
       </c>
       <c r="Q13" t="n">
-        <v>6928</v>
+        <v>6378</v>
       </c>
       <c r="R13" t="n">
-        <v>5502</v>
+        <v>5002</v>
       </c>
       <c r="S13" t="n">
-        <v>4290</v>
+        <v>3865</v>
       </c>
       <c r="T13" t="n">
-        <v>2195</v>
+        <v>1901</v>
       </c>
       <c r="U13" t="n">
-        <v>690</v>
+        <v>566</v>
       </c>
       <c r="V13" t="n">
         <v>13250</v>
@@ -18058,25 +18058,25 @@
         <v>14</v>
       </c>
       <c r="O17" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="P17" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="Q17" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="R17" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="S17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="U17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17" t="n">
         <v>473</v>
@@ -18478,19 +18478,19 @@
         <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T22" t="n">
         <v>1</v>
@@ -18562,25 +18562,25 @@
         <v>15</v>
       </c>
       <c r="O23" t="n">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="P23" t="n">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Q23" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="R23" t="n">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="S23" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="T23" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="U23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V23" t="n">
         <v>450</v>
@@ -18646,22 +18646,22 @@
         <v>25</v>
       </c>
       <c r="O24" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="P24" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="Q24" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="R24" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="S24" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="T24" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="U24" t="n">
         <v>8</v>
@@ -18730,19 +18730,19 @@
         <v>8</v>
       </c>
       <c r="O25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T25" t="n">
         <v>1</v>
@@ -18814,22 +18814,22 @@
         <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="P26" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Q26" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R26" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="S26" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U26" t="n">
         <v>3</v>
@@ -18898,25 +18898,25 @@
         <v>76</v>
       </c>
       <c r="O27" t="n">
-        <v>532</v>
+        <v>494</v>
       </c>
       <c r="P27" t="n">
-        <v>493</v>
+        <v>455</v>
       </c>
       <c r="Q27" t="n">
-        <v>473</v>
+        <v>435</v>
       </c>
       <c r="R27" t="n">
-        <v>400</v>
+        <v>366</v>
       </c>
       <c r="S27" t="n">
-        <v>317</v>
+        <v>286</v>
       </c>
       <c r="T27" t="n">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="U27" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="V27" t="n">
         <v>708</v>
@@ -18982,22 +18982,22 @@
         <v>17</v>
       </c>
       <c r="O28" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="P28" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="Q28" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="R28" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="S28" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="T28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U28" t="n">
         <v>3</v>
@@ -19066,25 +19066,25 @@
         <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P29" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q29" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="R29" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S29" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T29" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="U29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V29" t="n">
         <v>239</v>
@@ -19234,7 +19234,7 @@
         <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P31" t="n">
         <v>2</v>
@@ -19402,22 +19402,22 @@
         <v>5</v>
       </c>
       <c r="O33" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P33" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Q33" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="R33" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="S33" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="T33" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U33" t="n">
         <v>1</v>
@@ -19486,25 +19486,25 @@
         <v>21</v>
       </c>
       <c r="O34" t="n">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="P34" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q34" t="n">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="R34" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="S34" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="T34" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="U34" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V34" t="n">
         <v>585</v>
@@ -19570,25 +19570,25 @@
         <v>13</v>
       </c>
       <c r="O35" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="P35" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="Q35" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="R35" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="S35" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="T35" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="U35" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="V35" t="n">
         <v>117</v>
@@ -19738,25 +19738,25 @@
         <v>32</v>
       </c>
       <c r="O37" t="n">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="P37" t="n">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="Q37" t="n">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="R37" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="S37" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="T37" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="U37" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V37" t="n">
         <v>355</v>
@@ -19822,25 +19822,25 @@
         <v>145</v>
       </c>
       <c r="O38" t="n">
-        <v>943</v>
+        <v>891</v>
       </c>
       <c r="P38" t="n">
-        <v>837</v>
+        <v>787</v>
       </c>
       <c r="Q38" t="n">
-        <v>799</v>
+        <v>750</v>
       </c>
       <c r="R38" t="n">
-        <v>672</v>
+        <v>627</v>
       </c>
       <c r="S38" t="n">
-        <v>543</v>
+        <v>503</v>
       </c>
       <c r="T38" t="n">
-        <v>278</v>
+        <v>249</v>
       </c>
       <c r="U38" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="V38" t="n">
         <v>1432</v>
@@ -19990,25 +19990,25 @@
         <v>11</v>
       </c>
       <c r="O40" t="n">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="P40" t="n">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="Q40" t="n">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="R40" t="n">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="S40" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="T40" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="U40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V40" t="n">
         <v>478</v>
@@ -20158,22 +20158,22 @@
         <v>8</v>
       </c>
       <c r="O42" t="n">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="P42" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Q42" t="n">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="R42" t="n">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="S42" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="T42" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="U42" t="n">
         <v>6</v>
@@ -20578,25 +20578,25 @@
         <v>40</v>
       </c>
       <c r="O47" t="n">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="P47" t="n">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="Q47" t="n">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="R47" t="n">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="S47" t="n">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="T47" t="n">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="U47" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="V47" t="n">
         <v>784</v>
@@ -20662,25 +20662,25 @@
         <v>31</v>
       </c>
       <c r="O48" t="n">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="P48" t="n">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="Q48" t="n">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="R48" t="n">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="S48" t="n">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="T48" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="U48" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V48" t="n">
         <v>405</v>
@@ -21460,22 +21460,22 @@
         <v>16</v>
       </c>
       <c r="O2" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P2" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q2" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="S2" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U2" t="n">
         <v>13</v>
@@ -21544,22 +21544,22 @@
         <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="P3" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="Q3" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="R3" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="S3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="T3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="U3" t="n">
         <v>10</v>
@@ -21628,13 +21628,13 @@
         <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R4" t="n">
         <v>14</v>
@@ -21712,22 +21712,22 @@
         <v>3360</v>
       </c>
       <c r="O5" t="n">
-        <v>3845</v>
+        <v>3712</v>
       </c>
       <c r="P5" t="n">
-        <v>2234</v>
+        <v>2135</v>
       </c>
       <c r="Q5" t="n">
-        <v>1805</v>
+        <v>1719</v>
       </c>
       <c r="R5" t="n">
-        <v>892</v>
+        <v>845</v>
       </c>
       <c r="S5" t="n">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="T5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="U5" t="n">
         <v>2</v>
@@ -21796,22 +21796,22 @@
         <v>375</v>
       </c>
       <c r="O6" t="n">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="P6" t="n">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="Q6" t="n">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="R6" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="S6" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="T6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -21964,19 +21964,19 @@
         <v>211</v>
       </c>
       <c r="O8" t="n">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="P8" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="Q8" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="R8" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -22048,19 +22048,19 @@
         <v>4062</v>
       </c>
       <c r="O9" t="n">
-        <v>4913</v>
+        <v>4796</v>
       </c>
       <c r="P9" t="n">
-        <v>2302</v>
+        <v>2236</v>
       </c>
       <c r="Q9" t="n">
-        <v>1705</v>
+        <v>1654</v>
       </c>
       <c r="R9" t="n">
-        <v>672</v>
+        <v>653</v>
       </c>
       <c r="S9" t="n">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="T9" t="n">
         <v>24</v>
@@ -22216,19 +22216,19 @@
         <v>899</v>
       </c>
       <c r="O11" t="n">
-        <v>1374</v>
+        <v>1342</v>
       </c>
       <c r="P11" t="n">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="Q11" t="n">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="R11" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="S11" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="T11" t="n">
         <v>8</v>
@@ -22384,13 +22384,13 @@
         <v>6</v>
       </c>
       <c r="O13" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R13" t="n">
         <v>77</v>
@@ -25366,22 +25366,22 @@
         <v>178</v>
       </c>
       <c r="O35" t="n">
-        <v>357</v>
+        <v>323</v>
       </c>
       <c r="P35" t="n">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="Q35" t="n">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="R35" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="S35" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="T35" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="U35" t="n">
         <v>12</v>
@@ -25786,25 +25786,25 @@
         <v>111</v>
       </c>
       <c r="O40" t="n">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="P40" t="n">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="Q40" t="n">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="R40" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="S40" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T40" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="U40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V40" t="n">
         <v>2041</v>
@@ -25954,25 +25954,25 @@
         <v>18</v>
       </c>
       <c r="O42" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="P42" t="n">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="Q42" t="n">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="R42" t="n">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="S42" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="T42" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="U42" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V42" t="n">
         <v>909</v>
@@ -26038,22 +26038,22 @@
         <v>7</v>
       </c>
       <c r="O43" t="n">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="P43" t="n">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="Q43" t="n">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="R43" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="S43" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="T43" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="U43" t="n">
         <v>26</v>
@@ -27088,22 +27088,22 @@
         <v>8</v>
       </c>
       <c r="O4" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="P4" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="Q4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -27256,13 +27256,13 @@
         <v>9</v>
       </c>
       <c r="O6" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Q6" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R6" t="n">
         <v>50</v>
@@ -27424,19 +27424,19 @@
         <v>292</v>
       </c>
       <c r="O8" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="P8" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q8" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R8" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="S8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T8" t="n">
         <v>52</v>
@@ -29566,22 +29566,22 @@
         <v>7</v>
       </c>
       <c r="O2" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="P2" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="Q2" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="R2" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S2" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U2" t="n">
         <v>3</v>
@@ -29650,19 +29650,19 @@
         <v>23</v>
       </c>
       <c r="O3" t="n">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="P3" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="Q3" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="R3" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="S3" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="T3" t="n">
         <v>13</v>
@@ -29818,25 +29818,25 @@
         <v>434</v>
       </c>
       <c r="O5" t="n">
-        <v>4431</v>
+        <v>4335</v>
       </c>
       <c r="P5" t="n">
-        <v>2659</v>
+        <v>2568</v>
       </c>
       <c r="Q5" t="n">
-        <v>2200</v>
+        <v>2117</v>
       </c>
       <c r="R5" t="n">
-        <v>1163</v>
+        <v>1087</v>
       </c>
       <c r="S5" t="n">
-        <v>636</v>
+        <v>575</v>
       </c>
       <c r="T5" t="n">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="U5" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="V5" t="n">
         <v>28452</v>
@@ -29902,25 +29902,25 @@
         <v>62</v>
       </c>
       <c r="O6" t="n">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="P6" t="n">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="Q6" t="n">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="R6" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="S6" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="T6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>3886</v>
@@ -30070,22 +30070,22 @@
         <v>73</v>
       </c>
       <c r="O8" t="n">
-        <v>1709</v>
+        <v>1702</v>
       </c>
       <c r="P8" t="n">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="Q8" t="n">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="R8" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="S8" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="T8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -30322,25 +30322,25 @@
         <v>28</v>
       </c>
       <c r="O11" t="n">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="P11" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="Q11" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="R11" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="S11" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="T11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>2574</v>
@@ -30490,25 +30490,25 @@
         <v>170</v>
       </c>
       <c r="O13" t="n">
-        <v>2355</v>
+        <v>2320</v>
       </c>
       <c r="P13" t="n">
-        <v>1237</v>
+        <v>1208</v>
       </c>
       <c r="Q13" t="n">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="R13" t="n">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="S13" t="n">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="T13" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="U13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V13" t="n">
         <v>25688</v>
@@ -30574,19 +30574,19 @@
         <v>42</v>
       </c>
       <c r="O14" t="n">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="P14" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="Q14" t="n">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="R14" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="S14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T14" t="n">
         <v>6</v>
@@ -31204,25 +31204,25 @@
         <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="Q4" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="R4" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="S4" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="T4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V4" t="n">
         <v>179</v>
@@ -32548,25 +32548,25 @@
         <v>6</v>
       </c>
       <c r="O20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Q20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="S20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
         <v>46</v>
@@ -32632,25 +32632,25 @@
         <v>4</v>
       </c>
       <c r="O21" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P21" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Q21" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="R21" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="S21" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="T21" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="U21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V21" t="n">
         <v>537</v>
@@ -32716,7 +32716,7 @@
         <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P22" t="n">
         <v>184</v>
@@ -32800,25 +32800,25 @@
         <v>26</v>
       </c>
       <c r="O23" t="n">
-        <v>1897</v>
+        <v>1891</v>
       </c>
       <c r="P23" t="n">
-        <v>1443</v>
+        <v>1438</v>
       </c>
       <c r="Q23" t="n">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="R23" t="n">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="S23" t="n">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="T23" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="U23" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="V23" t="n">
         <v>5769</v>
@@ -32884,22 +32884,22 @@
         <v>47</v>
       </c>
       <c r="O24" t="n">
-        <v>1286</v>
+        <v>1278</v>
       </c>
       <c r="P24" t="n">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="Q24" t="n">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="R24" t="n">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="S24" t="n">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="T24" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="U24" t="n">
         <v>106</v>
@@ -33136,13 +33136,13 @@
         <v>104</v>
       </c>
       <c r="O27" t="n">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="P27" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q27" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R27" t="n">
         <v>35</v>
@@ -33388,25 +33388,25 @@
         <v>3781</v>
       </c>
       <c r="O30" t="n">
-        <v>31452</v>
+        <v>31199</v>
       </c>
       <c r="P30" t="n">
-        <v>17130</v>
+        <v>16927</v>
       </c>
       <c r="Q30" t="n">
-        <v>13499</v>
+        <v>13318</v>
       </c>
       <c r="R30" t="n">
-        <v>7093</v>
+        <v>6959</v>
       </c>
       <c r="S30" t="n">
-        <v>4313</v>
+        <v>4216</v>
       </c>
       <c r="T30" t="n">
-        <v>1524</v>
+        <v>1478</v>
       </c>
       <c r="U30" t="n">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="V30" t="n">
         <v>201345</v>
@@ -33472,25 +33472,25 @@
         <v>248</v>
       </c>
       <c r="O31" t="n">
-        <v>798</v>
+        <v>788</v>
       </c>
       <c r="P31" t="n">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="Q31" t="n">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="R31" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="S31" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="T31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V31" t="n">
         <v>4205</v>

--- a/summary_stats/chuuchuu_summary_2025_08.xlsx
+++ b/summary_stats/chuuchuu_summary_2025_08.xlsx
@@ -14627,7 +14627,7 @@
         </is>
       </c>
       <c r="J180" t="n">
-        <v>1569</v>
+        <v>1572</v>
       </c>
       <c r="K180" t="n">
         <v>0</v>
@@ -14639,28 +14639,28 @@
         <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U180" t="n">
-        <v>1569</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="181">
@@ -14706,7 +14706,7 @@
         </is>
       </c>
       <c r="J181" t="n">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="K181" t="n">
         <v>0</v>
@@ -14718,28 +14718,28 @@
         <v>16</v>
       </c>
       <c r="N181" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="O181" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="P181" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="Q181" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="R181" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="S181" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="T181" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="U181" t="n">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="182">
